--- a/restos.xlsx
+++ b/restos.xlsx
@@ -55384,13 +55384,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{848A4E03-A3A4-456B-833F-B6CE9B5C20F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B83B2EB7-5FA5-4401-9F2B-91AB4200891B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D9BA03-E1B7-45F4-AF92-B16A677BB360}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FBA08EF-CA25-4038-89B5-E8A25E90F42E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC28E1BB-02E4-4BCB-838E-D15CC12E2742}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC5007B0-140E-48DC-9E44-1B35A746815D}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -55384,13 +55384,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B83B2EB7-5FA5-4401-9F2B-91AB4200891B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DBB914C-A893-45C7-A4A2-2BFCB877BE61}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FBA08EF-CA25-4038-89B5-E8A25E90F42E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C860D57-5782-4EBC-97DF-DAE8062A870C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC5007B0-140E-48DC-9E44-1B35A746815D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89B69F17-26E9-45F0-935E-C9C87671F36F}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C804802F-62BC-4BB2-98EB-78CC7C7CDE02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134E88CE-42BF-4479-838D-7F59E74377A1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F10094E-DF75-461F-829D-8E1B44897AE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E6F0C3-2C4C-4551-9064-0CEA765390D8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBA07D4E-45A1-4EAA-8CDF-36F0D325D8D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE376E2-6650-4666-8D26-DF70AA7788E9}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134E88CE-42BF-4479-838D-7F59E74377A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECE0F1CF-0C7D-4751-B053-088A3BF4E4C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E6F0C3-2C4C-4551-9064-0CEA765390D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3078EF0A-A0C3-458F-89A5-712A566DBA6C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACE376E2-6650-4666-8D26-DF70AA7788E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BF5E4C6-9022-4C54-BDB6-5278164D2B97}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -55384,13 +55384,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EAC3EC0-B65B-4E43-9C08-63037E8B50F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBE7AA0B-0FA2-4C70-8B97-18443C35D8A7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70B70EF7-285E-41AE-93AB-C5B4EF3C47D6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF23F52C-8121-4857-A8C3-50B639470488}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D28BEFBB-72B9-4FCE-8444-9EA010C76C6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{530591B9-C9B5-48EC-BDD0-954252D15EA4}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FAC376-7E52-4CB8-A144-CB9371FCB60A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6155A34-3B57-4253-A425-7BD676AE59B7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E855ACE5-C059-4788-8C1D-34B6E37654F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380A27B-2D7E-4002-B459-EBE5044FFD9F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{997F833B-4DC6-467B-AD6C-88FF8D15237A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D9CF7E2-B40D-410E-9074-10945FA93BCC}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6155A34-3B57-4253-A425-7BD676AE59B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAFC3CF2-08B3-4D15-882C-6B0BBFCA97B5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5380A27B-2D7E-4002-B459-EBE5044FFD9F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9462631-6499-4C1A-8B40-8D442C38DA1C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D9CF7E2-B40D-410E-9074-10945FA93BCC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE2C9DF-61C1-47B8-981E-A6BA85493504}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -1243,7 +1243,7 @@
     <t>130012843</t>
   </si>
   <si>
-    <t>UP BRASIL ADMINISTRACAO E SERVICOS LTDA.</t>
+    <t>UP BRASIL ADMINISTRACAO SERVICOS E INSTITUICAO DE PAGAMENTO LTDA</t>
   </si>
   <si>
     <t>02.959.392/0001-46</t>
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAFC3CF2-08B3-4D15-882C-6B0BBFCA97B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93AFCA08-C5DF-4833-9297-2982A7DF6FD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9462631-6499-4C1A-8B40-8D442C38DA1C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887386E8-1ED2-4B8B-8BEC-B2A916144E34}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADE2C9DF-61C1-47B8-981E-A6BA85493504}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B1C188-6609-4A17-8760-0F8E441FEA8F}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -56831,13 +56831,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93AFCA08-C5DF-4833-9297-2982A7DF6FD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88F22AEB-069C-4BEC-876C-B5ADF03051C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{887386E8-1ED2-4B8B-8BEC-B2A916144E34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA4A1B73-24F3-4841-A4EF-842105C25A22}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9B1C188-6609-4A17-8760-0F8E441FEA8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8B87560-5951-4897-B6E6-7EF9FC49024F}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -57059,13 +57059,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2278808F-D869-4933-8126-83893342E84E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73619CDA-8ED7-4E92-862D-929432DECEC4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{777524A6-FFE4-4FF8-951F-2909FB4CE0F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE7F299-DF40-4E73-85F9-A8D61A91F2C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81A72BFF-ABE9-4ACF-B4A4-CA608B06B809}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA173F75-F8DD-4A7F-A821-338D71F5C5DB}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -57059,13 +57059,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73619CDA-8ED7-4E92-862D-929432DECEC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0159399-BCBA-40E8-B5C6-58DD04828540}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FE7F299-DF40-4E73-85F9-A8D61A91F2C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15A67E25-F5F2-48F8-B5D7-39BAA83CEE8B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA173F75-F8DD-4A7F-A821-338D71F5C5DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97E01656-C2C4-4239-B4BB-E96991531D3C}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -59260,13 +59260,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF867B11-4F96-4539-881D-67645918DFA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A3608A6-8BFF-46E0-939D-3C72A68A9EA8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532B9E83-08A7-4643-92D5-55106836DD19}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D26E7635-884B-41DB-B6AA-2B2FCFA304A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D50C6D48-B877-4913-BDEA-6E12B0964BE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78586F2F-CAD8-47B0-8169-1E746678C5C6}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -43017,7 +43017,7 @@
         <v>5927</v>
       </c>
       <c r="V363" s="6">
-        <v>-693596</v>
+        <v>46259</v>
       </c>
       <c r="W363" s="4" t="s">
         <v>405</v>
@@ -44877,7 +44877,7 @@
         <v>5925</v>
       </c>
       <c r="V379" s="6">
-        <v>-693596</v>
+        <v>46259</v>
       </c>
       <c r="W379" s="4" t="s">
         <v>405</v>
@@ -44994,7 +44994,7 @@
         <v>5926</v>
       </c>
       <c r="V380" s="6">
-        <v>-693596</v>
+        <v>46259</v>
       </c>
       <c r="W380" s="4" t="s">
         <v>405</v>
@@ -45111,7 +45111,7 @@
         <v>5928</v>
       </c>
       <c r="V381" s="6">
-        <v>-693596</v>
+        <v>46259</v>
       </c>
       <c r="W381" s="4" t="s">
         <v>405</v>
@@ -59734,13 +59734,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1597378E-AA14-4637-BE04-0510EB2BA2F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE5552B-2D47-4CC8-863D-19EE599C98BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED33E4A-98B0-48AA-8A19-B502682CABEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E772B3E-46AB-45AD-807D-16116706FD9D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D15BEBD7-9675-4AB1-A7F6-6CD4E122A0F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7374DE-161A-4C22-AEDB-48D1F95128E8}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4541" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4541" uniqueCount="442">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -1225,9 +1225,6 @@
     <t>154545</t>
   </si>
   <si>
-    <t>Pendente de transmissão aos bancos</t>
-  </si>
-  <si>
     <t>221384</t>
   </si>
   <si>
@@ -1467,7 +1464,7 @@
     <row r="1" s="1" customFormat="1" ht="8.5328" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="31.4647" customHeight="1">
       <c r="D2" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
@@ -43020,7 +43017,7 @@
         <v>46259</v>
       </c>
       <c r="W363" s="4" t="s">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="X363" s="5">
         <v>59.92</v>
@@ -44880,7 +44877,7 @@
         <v>46259</v>
       </c>
       <c r="W379" s="4" t="s">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="X379" s="5">
         <v>201.23</v>
@@ -44898,7 +44895,7 @@
         <v>47</v>
       </c>
       <c r="AC379" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD379" s="3">
         <v>8</v>
@@ -44997,7 +44994,7 @@
         <v>46259</v>
       </c>
       <c r="W380" s="4" t="s">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="X380" s="5">
         <v>233.63</v>
@@ -45015,7 +45012,7 @@
         <v>47</v>
       </c>
       <c r="AC380" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD380" s="3">
         <v>8</v>
@@ -45114,7 +45111,7 @@
         <v>46259</v>
       </c>
       <c r="W381" s="4" t="s">
-        <v>405</v>
+        <v>135</v>
       </c>
       <c r="X381" s="5">
         <v>434.86</v>
@@ -45132,7 +45129,7 @@
         <v>47</v>
       </c>
       <c r="AC381" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AD381" s="3">
         <v>8</v>
@@ -48283,7 +48280,7 @@
         <v>4434</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E409" s="4" t="s">
         <v>128</v>
@@ -48398,13 +48395,13 @@
         <v>4434</v>
       </c>
       <c r="D410" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E410" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E410" s="4" t="s">
+      <c r="F410" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="F410" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="G410" s="4" t="s">
         <v>96</v>
@@ -48416,7 +48413,7 @@
         <v>2025</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K410" s="3">
         <v>9.47884e6</v>
@@ -48513,13 +48510,13 @@
         <v>4434</v>
       </c>
       <c r="D411" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E411" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E411" s="4" t="s">
+      <c r="F411" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="F411" s="4" t="s">
-        <v>409</v>
       </c>
       <c r="G411" s="4" t="s">
         <v>96</v>
@@ -48531,7 +48528,7 @@
         <v>2025</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="K411" s="3">
         <v>9.47884e6</v>
@@ -48628,7 +48625,7 @@
         <v>4434</v>
       </c>
       <c r="D412" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E412" s="4" t="s">
         <v>125</v>
@@ -48743,13 +48740,13 @@
         <v>4434</v>
       </c>
       <c r="D413" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E413" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F413" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F413" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G413" s="4" t="s">
         <v>96</v>
@@ -48761,7 +48758,7 @@
         <v>2025</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K413" s="3">
         <v>9.470167e6</v>
@@ -48858,13 +48855,13 @@
         <v>4434</v>
       </c>
       <c r="D414" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E414" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F414" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F414" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G414" s="4" t="s">
         <v>96</v>
@@ -48876,7 +48873,7 @@
         <v>2025</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K414" s="3">
         <v>9.470167e6</v>
@@ -48915,22 +48912,22 @@
         <v>46042</v>
       </c>
       <c r="W414" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="X414" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y414" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z414" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA414" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB414" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="X414" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y414" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z414" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA414" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB414" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="AC414" s="4" t="s">
         <v>153</v>
@@ -48977,13 +48974,13 @@
         <v>4434</v>
       </c>
       <c r="D415" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E415" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F415" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F415" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G415" s="4" t="s">
         <v>96</v>
@@ -48995,7 +48992,7 @@
         <v>2025</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K415" s="3">
         <v>9.470167e6</v>
@@ -49049,7 +49046,7 @@
         <v>0</v>
       </c>
       <c r="AB415" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC415" s="4" t="s">
         <v>153</v>
@@ -49096,7 +49093,7 @@
         <v>4434</v>
       </c>
       <c r="D416" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E416" s="4" t="s">
         <v>402</v>
@@ -49211,7 +49208,7 @@
         <v>4434</v>
       </c>
       <c r="D417" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E417" s="4" t="s">
         <v>402</v>
@@ -49330,7 +49327,7 @@
         <v>4434</v>
       </c>
       <c r="D418" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E418" s="4" t="s">
         <v>173</v>
@@ -49443,7 +49440,7 @@
         <v>4434</v>
       </c>
       <c r="D419" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E419" s="4" t="s">
         <v>173</v>
@@ -49556,7 +49553,7 @@
         <v>4434</v>
       </c>
       <c r="D420" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E420" s="4" t="s">
         <v>173</v>
@@ -49673,7 +49670,7 @@
         <v>4434</v>
       </c>
       <c r="D421" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E421" s="4" t="s">
         <v>173</v>
@@ -49786,7 +49783,7 @@
         <v>4434</v>
       </c>
       <c r="D422" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E422" s="4" t="s">
         <v>173</v>
@@ -49899,7 +49896,7 @@
         <v>4434</v>
       </c>
       <c r="D423" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E423" s="4" t="s">
         <v>173</v>
@@ -50016,7 +50013,7 @@
         <v>4434</v>
       </c>
       <c r="D424" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E424" s="4" t="s">
         <v>173</v>
@@ -50133,7 +50130,7 @@
         <v>4434</v>
       </c>
       <c r="D425" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E425" s="4" t="s">
         <v>173</v>
@@ -50248,7 +50245,7 @@
         <v>4434</v>
       </c>
       <c r="D426" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E426" s="4" t="s">
         <v>173</v>
@@ -50363,7 +50360,7 @@
         <v>4434</v>
       </c>
       <c r="D427" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E427" s="4" t="s">
         <v>173</v>
@@ -50482,7 +50479,7 @@
         <v>4434</v>
       </c>
       <c r="D428" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E428" s="4" t="s">
         <v>173</v>
@@ -50597,7 +50594,7 @@
         <v>4434</v>
       </c>
       <c r="D429" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E429" s="4" t="s">
         <v>173</v>
@@ -50716,7 +50713,7 @@
         <v>4434</v>
       </c>
       <c r="D430" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E430" s="4" t="s">
         <v>173</v>
@@ -50831,7 +50828,7 @@
         <v>4434</v>
       </c>
       <c r="D431" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E431" s="4" t="s">
         <v>173</v>
@@ -50946,7 +50943,7 @@
         <v>4434</v>
       </c>
       <c r="D432" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E432" s="4" t="s">
         <v>173</v>
@@ -51061,7 +51058,7 @@
         <v>4434</v>
       </c>
       <c r="D433" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E433" s="4" t="s">
         <v>173</v>
@@ -51176,7 +51173,7 @@
         <v>4434</v>
       </c>
       <c r="D434" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E434" s="4" t="s">
         <v>173</v>
@@ -51295,7 +51292,7 @@
         <v>4434</v>
       </c>
       <c r="D435" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E435" s="4" t="s">
         <v>173</v>
@@ -51414,7 +51411,7 @@
         <v>4434</v>
       </c>
       <c r="D436" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E436" s="4" t="s">
         <v>173</v>
@@ -51533,7 +51530,7 @@
         <v>4434</v>
       </c>
       <c r="D437" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E437" s="4" t="s">
         <v>173</v>
@@ -51646,7 +51643,7 @@
         <v>4434</v>
       </c>
       <c r="D438" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E438" s="4" t="s">
         <v>173</v>
@@ -51763,7 +51760,7 @@
         <v>4434</v>
       </c>
       <c r="D439" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E439" s="4" t="s">
         <v>173</v>
@@ -51876,7 +51873,7 @@
         <v>4434</v>
       </c>
       <c r="D440" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E440" s="4" t="s">
         <v>173</v>
@@ -51989,7 +51986,7 @@
         <v>4434</v>
       </c>
       <c r="D441" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E441" s="4" t="s">
         <v>194</v>
@@ -52104,7 +52101,7 @@
         <v>4434</v>
       </c>
       <c r="D442" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E442" s="4" t="s">
         <v>194</v>
@@ -52219,7 +52216,7 @@
         <v>4434</v>
       </c>
       <c r="D443" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E443" s="4" t="s">
         <v>194</v>
@@ -52338,13 +52335,13 @@
         <v>4434</v>
       </c>
       <c r="D444" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E444" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="F444" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="F444" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="G444" s="4" t="s">
         <v>106</v>
@@ -52356,7 +52353,7 @@
         <v>2025</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K444" s="3">
         <v>9.331944e6</v>
@@ -52451,13 +52448,13 @@
         <v>4434</v>
       </c>
       <c r="D445" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E445" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="F445" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="F445" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="G445" s="4" t="s">
         <v>106</v>
@@ -52469,7 +52466,7 @@
         <v>2025</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K445" s="3">
         <v>9.331944e6</v>
@@ -52564,7 +52561,7 @@
         <v>4434</v>
       </c>
       <c r="D446" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E446" s="4" t="s">
         <v>200</v>
@@ -52679,7 +52676,7 @@
         <v>4434</v>
       </c>
       <c r="D447" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E447" s="4" t="s">
         <v>200</v>
@@ -52794,7 +52791,7 @@
         <v>4434</v>
       </c>
       <c r="D448" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E448" s="4" t="s">
         <v>200</v>
@@ -52907,7 +52904,7 @@
         <v>4434</v>
       </c>
       <c r="D449" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E449" s="4" t="s">
         <v>200</v>
@@ -53020,7 +53017,7 @@
         <v>4434</v>
       </c>
       <c r="D450" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E450" s="4" t="s">
         <v>200</v>
@@ -53135,7 +53132,7 @@
         <v>4434</v>
       </c>
       <c r="D451" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E451" s="4" t="s">
         <v>200</v>
@@ -53250,7 +53247,7 @@
         <v>4434</v>
       </c>
       <c r="D452" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E452" s="4" t="s">
         <v>200</v>
@@ -53365,7 +53362,7 @@
         <v>4434</v>
       </c>
       <c r="D453" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E453" s="4" t="s">
         <v>200</v>
@@ -53480,16 +53477,16 @@
         <v>4435</v>
       </c>
       <c r="D454" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E454" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E454" s="4" t="s">
+      <c r="F454" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F454" s="4" t="s">
+      <c r="G454" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G454" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="H454" s="3">
         <v>1422</v>
@@ -53498,7 +53495,7 @@
         <v>2025</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K454" s="3">
         <v>9.470154e6</v>
@@ -53595,16 +53592,16 @@
         <v>4435</v>
       </c>
       <c r="D455" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E455" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E455" s="4" t="s">
+      <c r="F455" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F455" s="4" t="s">
+      <c r="G455" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G455" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="H455" s="3">
         <v>1426</v>
@@ -53613,7 +53610,7 @@
         <v>2025</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K455" s="3">
         <v>9.470154e6</v>
@@ -53708,16 +53705,16 @@
         <v>4435</v>
       </c>
       <c r="D456" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E456" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="E456" s="4" t="s">
+      <c r="F456" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="F456" s="4" t="s">
+      <c r="G456" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="G456" s="4" t="s">
-        <v>423</v>
       </c>
       <c r="H456" s="3">
         <v>1582</v>
@@ -53726,7 +53723,7 @@
         <v>2025</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K456" s="3">
         <v>9.470154e6</v>
@@ -53823,13 +53820,13 @@
         <v>4435</v>
       </c>
       <c r="D457" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E457" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F457" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F457" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G457" s="4" t="s">
         <v>96</v>
@@ -53841,7 +53838,7 @@
         <v>2025</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K457" s="3">
         <v>9.470167e6</v>
@@ -53938,13 +53935,13 @@
         <v>4435</v>
       </c>
       <c r="D458" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E458" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F458" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F458" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G458" s="4" t="s">
         <v>96</v>
@@ -53956,7 +53953,7 @@
         <v>2025</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K458" s="3">
         <v>9.470167e6</v>
@@ -53995,22 +53992,22 @@
         <v>46042</v>
       </c>
       <c r="W458" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="X458" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y458" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z458" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA458" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB458" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="X458" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y458" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z458" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA458" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB458" s="4" t="s">
-        <v>415</v>
       </c>
       <c r="AC458" s="4" t="s">
         <v>153</v>
@@ -54057,13 +54054,13 @@
         <v>4435</v>
       </c>
       <c r="D459" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E459" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F459" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F459" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G459" s="4" t="s">
         <v>96</v>
@@ -54075,7 +54072,7 @@
         <v>2025</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K459" s="3">
         <v>9.470167e6</v>
@@ -54129,7 +54126,7 @@
         <v>0</v>
       </c>
       <c r="AB459" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AC459" s="4" t="s">
         <v>153</v>
@@ -54176,13 +54173,13 @@
         <v>4435</v>
       </c>
       <c r="D460" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E460" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="F460" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="F460" s="4" t="s">
-        <v>412</v>
       </c>
       <c r="G460" s="4" t="s">
         <v>96</v>
@@ -54194,7 +54191,7 @@
         <v>2025</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="K460" s="3">
         <v>9.470167e6</v>
@@ -54289,7 +54286,7 @@
         <v>4435</v>
       </c>
       <c r="D461" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E461" s="4" t="s">
         <v>402</v>
@@ -54402,7 +54399,7 @@
         <v>4435</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E462" s="4" t="s">
         <v>402</v>
@@ -54515,7 +54512,7 @@
         <v>4435</v>
       </c>
       <c r="D463" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E463" s="4" t="s">
         <v>173</v>
@@ -54630,7 +54627,7 @@
         <v>4435</v>
       </c>
       <c r="D464" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E464" s="4" t="s">
         <v>173</v>
@@ -54745,7 +54742,7 @@
         <v>4435</v>
       </c>
       <c r="D465" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E465" s="4" t="s">
         <v>173</v>
@@ -54864,7 +54861,7 @@
         <v>4435</v>
       </c>
       <c r="D466" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E466" s="4" t="s">
         <v>173</v>
@@ -54979,7 +54976,7 @@
         <v>4435</v>
       </c>
       <c r="D467" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E467" s="4" t="s">
         <v>173</v>
@@ -55094,7 +55091,7 @@
         <v>4435</v>
       </c>
       <c r="D468" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E468" s="4" t="s">
         <v>173</v>
@@ -55213,7 +55210,7 @@
         <v>4435</v>
       </c>
       <c r="D469" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E469" s="4" t="s">
         <v>173</v>
@@ -55332,7 +55329,7 @@
         <v>4435</v>
       </c>
       <c r="D470" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E470" s="4" t="s">
         <v>173</v>
@@ -55451,7 +55448,7 @@
         <v>4435</v>
       </c>
       <c r="D471" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E471" s="4" t="s">
         <v>173</v>
@@ -55570,7 +55567,7 @@
         <v>4435</v>
       </c>
       <c r="D472" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E472" s="4" t="s">
         <v>173</v>
@@ -55683,13 +55680,13 @@
         <v>4435</v>
       </c>
       <c r="D473" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E473" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F473" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F473" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="G473" s="4" t="s">
         <v>96</v>
@@ -55701,7 +55698,7 @@
         <v>2025</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K473" s="3">
         <v>9.445692e6</v>
@@ -55796,13 +55793,13 @@
         <v>4435</v>
       </c>
       <c r="D474" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E474" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F474" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F474" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="G474" s="4" t="s">
         <v>96</v>
@@ -55814,7 +55811,7 @@
         <v>2025</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K474" s="3">
         <v>9.445692e6</v>
@@ -55909,13 +55906,13 @@
         <v>4435</v>
       </c>
       <c r="D475" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E475" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F475" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F475" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="G475" s="4" t="s">
         <v>96</v>
@@ -55927,7 +55924,7 @@
         <v>2025</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K475" s="3">
         <v>9.445692e6</v>
@@ -55979,7 +55976,7 @@
         <v>0</v>
       </c>
       <c r="AB475" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC475" s="4" t="s">
         <v>400</v>
@@ -56026,13 +56023,13 @@
         <v>4435</v>
       </c>
       <c r="D476" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E476" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="F476" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="F476" s="4" t="s">
-        <v>425</v>
       </c>
       <c r="G476" s="4" t="s">
         <v>96</v>
@@ -56044,7 +56041,7 @@
         <v>2025</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="K476" s="3">
         <v>9.445692e6</v>
@@ -56096,7 +56093,7 @@
         <v>0</v>
       </c>
       <c r="AB476" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC476" s="4" t="s">
         <v>400</v>
@@ -56143,13 +56140,13 @@
         <v>4435</v>
       </c>
       <c r="D477" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E477" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F477" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F477" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G477" s="4" t="s">
         <v>106</v>
@@ -56161,7 +56158,7 @@
         <v>2025</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K477" s="3">
         <v>9.433849e6</v>
@@ -56258,13 +56255,13 @@
         <v>4435</v>
       </c>
       <c r="D478" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E478" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F478" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F478" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G478" s="4" t="s">
         <v>106</v>
@@ -56276,7 +56273,7 @@
         <v>2025</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K478" s="3">
         <v>9.433849e6</v>
@@ -56373,13 +56370,13 @@
         <v>4435</v>
       </c>
       <c r="D479" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E479" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F479" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F479" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G479" s="4" t="s">
         <v>106</v>
@@ -56391,7 +56388,7 @@
         <v>2025</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K479" s="3">
         <v>9.433849e6</v>
@@ -56488,13 +56485,13 @@
         <v>4435</v>
       </c>
       <c r="D480" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E480" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F480" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F480" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G480" s="4" t="s">
         <v>106</v>
@@ -56506,7 +56503,7 @@
         <v>2025</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K480" s="3">
         <v>9.433849e6</v>
@@ -56603,13 +56600,13 @@
         <v>4435</v>
       </c>
       <c r="D481" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E481" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F481" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F481" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G481" s="4" t="s">
         <v>106</v>
@@ -56621,7 +56618,7 @@
         <v>2025</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K481" s="3">
         <v>9.433849e6</v>
@@ -56675,7 +56672,7 @@
         <v>0</v>
       </c>
       <c r="AB481" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC481" s="4" t="s">
         <v>153</v>
@@ -56722,13 +56719,13 @@
         <v>4435</v>
       </c>
       <c r="D482" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E482" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F482" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F482" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G482" s="4" t="s">
         <v>106</v>
@@ -56740,7 +56737,7 @@
         <v>2025</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K482" s="3">
         <v>9.433849e6</v>
@@ -56794,7 +56791,7 @@
         <v>0</v>
       </c>
       <c r="AB482" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC482" s="4" t="s">
         <v>153</v>
@@ -56841,13 +56838,13 @@
         <v>4435</v>
       </c>
       <c r="D483" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E483" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F483" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F483" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G483" s="4" t="s">
         <v>106</v>
@@ -56859,7 +56856,7 @@
         <v>2025</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K483" s="3">
         <v>9.433849e6</v>
@@ -56913,7 +56910,7 @@
         <v>0</v>
       </c>
       <c r="AB483" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC483" s="4" t="s">
         <v>153</v>
@@ -56960,13 +56957,13 @@
         <v>4435</v>
       </c>
       <c r="D484" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E484" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="F484" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="F484" s="4" t="s">
-        <v>429</v>
       </c>
       <c r="G484" s="4" t="s">
         <v>106</v>
@@ -56978,7 +56975,7 @@
         <v>2025</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K484" s="3">
         <v>9.433849e6</v>
@@ -57032,7 +57029,7 @@
         <v>0</v>
       </c>
       <c r="AB484" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AC484" s="4" t="s">
         <v>153</v>
@@ -57079,7 +57076,7 @@
         <v>4435</v>
       </c>
       <c r="D485" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E485" s="4" t="s">
         <v>200</v>
@@ -57192,7 +57189,7 @@
         <v>4435</v>
       </c>
       <c r="D486" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E486" s="4" t="s">
         <v>200</v>
@@ -57305,7 +57302,7 @@
         <v>4435</v>
       </c>
       <c r="D487" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E487" s="4" t="s">
         <v>200</v>
@@ -57418,7 +57415,7 @@
         <v>4435</v>
       </c>
       <c r="D488" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E488" s="4" t="s">
         <v>200</v>
@@ -57535,7 +57532,7 @@
         <v>4435</v>
       </c>
       <c r="D489" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E489" s="4" t="s">
         <v>200</v>
@@ -57648,7 +57645,7 @@
         <v>4435</v>
       </c>
       <c r="D490" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E490" s="4" t="s">
         <v>200</v>
@@ -57761,7 +57758,7 @@
         <v>4435</v>
       </c>
       <c r="D491" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E491" s="4" t="s">
         <v>200</v>
@@ -57874,7 +57871,7 @@
         <v>4435</v>
       </c>
       <c r="D492" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E492" s="4" t="s">
         <v>200</v>
@@ -57987,7 +57984,7 @@
         <v>4435</v>
       </c>
       <c r="D493" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E493" s="4" t="s">
         <v>200</v>
@@ -58102,7 +58099,7 @@
         <v>4435</v>
       </c>
       <c r="D494" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E494" s="4" t="s">
         <v>200</v>
@@ -58217,7 +58214,7 @@
         <v>4447</v>
       </c>
       <c r="D495" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E495" s="4" t="s">
         <v>100</v>
@@ -58332,7 +58329,7 @@
         <v>4447</v>
       </c>
       <c r="D496" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E496" s="4" t="s">
         <v>100</v>
@@ -58447,7 +58444,7 @@
         <v>4447</v>
       </c>
       <c r="D497" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E497" s="4" t="s">
         <v>100</v>
@@ -58465,7 +58462,7 @@
         <v>2017</v>
       </c>
       <c r="J497" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K497" s="3">
         <v>9.043778e6</v>
@@ -58562,7 +58559,7 @@
         <v>4447</v>
       </c>
       <c r="D498" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E498" s="4" t="s">
         <v>100</v>
@@ -58677,7 +58674,7 @@
         <v>4447</v>
       </c>
       <c r="D499" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E499" s="4" t="s">
         <v>100</v>
@@ -58695,7 +58692,7 @@
         <v>2017</v>
       </c>
       <c r="J499" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K499" s="3">
         <v>9.043778e6</v>
@@ -58792,13 +58789,13 @@
         <v>4447</v>
       </c>
       <c r="D500" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E500" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F500" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="F500" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="G500" s="4" t="s">
         <v>96</v>
@@ -58907,13 +58904,13 @@
         <v>4447</v>
       </c>
       <c r="D501" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E501" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="F501" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="F501" s="4" t="s">
-        <v>435</v>
       </c>
       <c r="G501" s="4" t="s">
         <v>96</v>
@@ -59022,7 +59019,7 @@
         <v>4447</v>
       </c>
       <c r="D502" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E502" s="4" t="s">
         <v>173</v>
@@ -59137,13 +59134,13 @@
         <v>4447</v>
       </c>
       <c r="D503" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E503" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F503" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="F503" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="G503" s="4" t="s">
         <v>115</v>
@@ -59252,13 +59249,13 @@
         <v>4447</v>
       </c>
       <c r="D504" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E504" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="F504" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="F504" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="G504" s="4" t="s">
         <v>115</v>
@@ -59367,13 +59364,13 @@
         <v>4592</v>
       </c>
       <c r="D505" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E505" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E505" s="4" t="s">
+      <c r="F505" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="F505" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="G505" s="4" t="s">
         <v>297</v>
@@ -59385,7 +59382,7 @@
         <v>2012</v>
       </c>
       <c r="J505" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K505" s="3">
         <v>0</v>
@@ -59734,13 +59731,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BE5552B-2D47-4CC8-863D-19EE599C98BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2130AA-B74F-4053-B9D6-93869E752ED0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E772B3E-46AB-45AD-807D-16116706FD9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A4D96F-4178-49BA-B360-3B02F70E1AB3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC7374DE-161A-4C22-AEDB-48D1F95128E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55961EB1-A2A4-4024-B5AC-9FAEEB4B75FD}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -59731,13 +59731,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2130AA-B74F-4053-B9D6-93869E752ED0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F659F295-9DED-4A97-AACB-4477E289E3B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90A4D96F-4178-49BA-B360-3B02F70E1AB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CC1868-1E44-45FA-B831-C7F14F65A577}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55961EB1-A2A4-4024-B5AC-9FAEEB4B75FD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BC60AD-018C-4AED-8B9B-274DEEDEC387}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -59731,13 +59731,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F659F295-9DED-4A97-AACB-4477E289E3B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FBA239-18AD-4BE4-9AC7-67B8F15D62E4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CC1868-1E44-45FA-B831-C7F14F65A577}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD43C81-069B-4908-A127-8563580924AD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26BC60AD-018C-4AED-8B9B-274DEEDEC387}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFDFCBDB-F0E7-4C64-9092-40A1C64ED922}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -59731,13 +59731,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FBA239-18AD-4BE4-9AC7-67B8F15D62E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42983305-BB0B-47F1-B3BB-F7ACBB763960}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BD43C81-069B-4908-A127-8563580924AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{965AAF34-2C11-41F9-9474-775EBCC2E4B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFDFCBDB-F0E7-4C64-9092-40A1C64ED922}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F8973B-02B9-40BC-A804-FB17E09179B8}"/>
 </file>
--- a/restos.xlsx
+++ b/restos.xlsx
@@ -59731,13 +59731,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42983305-BB0B-47F1-B3BB-F7ACBB763960}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEB9BBA4-2CE1-42C1-9974-D53B79C72EAE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{965AAF34-2C11-41F9-9474-775EBCC2E4B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2123FC4-845C-471F-9607-E8CC8BA56AFE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{98F8973B-02B9-40BC-A804-FB17E09179B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32BD3B49-99FC-4F08-B6FE-395879FCAFA3}"/>
 </file>